--- a/engine/egch_study/EGCH_Valuation_Model_01092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_01092026.xlsx
@@ -1343,23 +1343,23 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>B5*'Assumptions'!C135/365</f>
+        <f>B5*'Assumptions'!C142/365</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>C5*'Assumptions'!C135/365</f>
+        <f>C5*'Assumptions'!C142/365</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>D5*'Assumptions'!C135/365</f>
+        <f>D5*'Assumptions'!C142/365</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>E5*'Assumptions'!C135/365</f>
+        <f>E5*'Assumptions'!C142/365</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>F5*'Assumptions'!C135/365</f>
+        <f>F5*'Assumptions'!C142/365</f>
         <v/>
       </c>
     </row>
@@ -1370,23 +1370,23 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>B6*'Assumptions'!C136/365</f>
+        <f>B6*'Assumptions'!C143/365</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>C6*'Assumptions'!C136/365</f>
+        <f>C6*'Assumptions'!C143/365</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>D6*'Assumptions'!C136/365</f>
+        <f>D6*'Assumptions'!C143/365</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>E6*'Assumptions'!C136/365</f>
+        <f>E6*'Assumptions'!C143/365</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>F6*'Assumptions'!C136/365</f>
+        <f>F6*'Assumptions'!C143/365</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>B6*'Assumptions'!C137/365</f>
+        <f>B6*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>C6*'Assumptions'!C137/365</f>
+        <f>C6*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>D6*'Assumptions'!C137/365</f>
+        <f>D6*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>E6*'Assumptions'!C137/365</f>
+        <f>E6*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>F6*'Assumptions'!C137/365</f>
+        <f>F6*'Assumptions'!C144/365</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2675,19 +2675,19 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.68</v>
+        <v>-2.7</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-2.78</v>
+        <v>-2.79</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-2.88</v>
+        <v>-2.89</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-2.94</v>
+        <v>-2.95</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-3.01</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="7">
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-1.14</v>
+        <v>-1.19</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-1.32</v>
+        <v>-1.37</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-1.5</v>
+        <v>-1.54</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1.62</v>
+        <v>-1.66</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-1.74</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="8">
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>-0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-0.3</v>
+        <v>-0.37</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-0.48</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="9">
@@ -2741,19 +2741,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.79</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2763,19 +2763,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.1961934433273287</v>
+        <v>0.1030999883383652</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>-1.244804084295214</v>
+        <v>-1.397694934111888</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>-0.6002745383210529</v>
+        <v>-0.6670180351027122</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2883,16 +2883,16 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Beta from the five-year weekly regression of the share against the published EGX30 index</t>
+          <t>The cost of debt at the company's own disclosed rates — 19.4% on the local facility, 11.7% in dollars on the project loan carried at local-equivalent cost on the derived currency path, 20.0% in year one gliding to 11.8% at the terminal</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>The lower bound of that regression's own 90% confidence interval</t>
+          <t>Every leg floored at the 23.00% sovereign ten-year yield — the company's own facilities print no spread above the policy rate, so no spread is added</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.2669072397816836</v>
+        <v>-1.062000234885711</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2902,16 +2902,16 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Gas at the realised price the company's own loss disclosure implies</t>
+          <t>Beta from the five-year weekly regression of the share against the published EGX30 index</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>The contract formula price in the operating agreement, which is higher</t>
+          <t>The lower bound of that regression's own 90% confidence interval</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>-2.487224805524408</v>
+        <v>0.1709154866519979</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2921,16 +2921,16 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>The new complex earning at half its derived nameplate in the terminal year</t>
+          <t>Gas at the realised price the company's own loss disclosure implies</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Seventy per cent, which is what a well-run nitrate line achieves</t>
+          <t>The contract formula price in the operating agreement, which is higher</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>-0.3228328758581689</v>
+        <v>-2.50809878104179</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -2940,16 +2940,16 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure at the company's own observed pre-project rate of 1.12% of revenue</t>
+          <t>The new complex earning at half its derived nameplate in the terminal year</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Replacement-rate maintenance: gross fixed assets at the disclosed 3.95% machinery depreciation rate, or 6.11% of revenue</t>
+          <t>Seventy per cent, which is what a well-run nitrate line achieves</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>-1.36355838815048</v>
+        <v>-0.3983876059568149</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -2959,16 +2959,16 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Terminal reinvestment of 38.9% of operating profit after tax, from growth over an 18% return on capital</t>
+          <t>Maintenance capital expenditure at the company's own observed pre-project rate of 1.12% of revenue</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>23.3%, from a 30% return on capital — the rate a newly completed plant earns on incremental capital while it is still filling</t>
+          <t>Replacement-rate maintenance: gross fixed assets at the disclosed 3.95% machinery depreciation rate, or 6.11% of revenue</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>-0.2765371741139211</v>
+        <v>-1.415814469979403</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -2978,24 +2978,43 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Project spending anchored on the observed run rate: the nine-month actual extended to a full year</t>
+          <t>Terminal reinvestment of 27.8% of operating profit after tax, from growth over an 18% return on capital</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>The faster profile the first issue of this study used, opening at EGP 3,000m</t>
+          <t>16.7%, from a 30% return on capital — the rate a newly completed plant earns on incremental capital while it is still filling</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>-0.7911730177131145</v>
+        <v>-0.3534762974524243</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="39" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Project spending anchored on the observed run rate: the nine-month actual extended to a full year</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>The faster profile the first issue of this study used, opening at EGP 3,000m</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>-0.8572462475446263</v>
+      </c>
+      <c r="D26" s="11">
+        <f>C26-$D$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="39" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Each row is a complete re-run of the model through the same case machinery with one component moved and everything else held. Column C is pasted class 3 and DOES NOT REDRAW; column D is a formula against the published answer so the gap can never drift from the values beside it.</t>
         </is>
@@ -3102,7 +3121,7 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>'Assumptions'!C91</f>
+        <f>'Assumptions'!C98</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -3396,7 +3415,7 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>'Assumptions'!C69</f>
+        <f>'Assumptions'!C76</f>
         <v/>
       </c>
     </row>
@@ -3701,7 +3720,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.0775073399054228</v>
+        <v>0.07750436005742409</v>
       </c>
     </row>
     <row r="26">
@@ -3721,7 +3740,7 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>'Assumptions'!C102</f>
+        <f>'Assumptions'!C109</f>
         <v/>
       </c>
     </row>
@@ -3732,7 +3751,7 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>'Assumptions'!C100*'Assumptions'!C92+'Assumptions'!C101*'Assumptions'!C98*(1-'Assumptions'!C99)</f>
+        <f>'Assumptions'!C107*'Assumptions'!C99+'Assumptions'!C108*'Assumptions'!C105*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
     </row>
@@ -3934,7 +3953,7 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>'Assumptions'!C91</f>
+        <f>'Assumptions'!C98</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -3950,7 +3969,7 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>'Assumptions'!C109</f>
+        <f>'Assumptions'!C116</f>
         <v/>
       </c>
       <c r="C15" s="9" t="inlineStr"/>
@@ -4046,7 +4065,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>-0.5572364806610506</v>
+        <v>-0.6254255245924404</v>
       </c>
     </row>
     <row r="24">
@@ -4056,7 +4075,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>3.585910769087703</v>
+        <v>3.427492145329595</v>
       </c>
     </row>
     <row r="25">
@@ -4122,7 +4141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4768,10 +4787,10 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Egyptian pounds per US dollar — FY2026/27</t>
+          <t>Egyptian pounds per US dollar, spot</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -4780,685 +4799,695 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>53.4853515625</v>
+        <v>49.79</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
+          <t>Market quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Egyptian pounds per US dollar — FY2027/28</t>
+          <t>Long-run United States inflation</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>EGP/US$</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>55.88801383972168</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>0.024</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
+          <t>Long-run United States inflation, the other leg of the purchasing-power wedge</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Egyptian pounds per US dollar — FY2028/29</t>
+          <t>Currency wedge — FY2026/27</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C40" s="16">
+        <f>(1+'Assumptions'!C84)/(1+'Assumptions'!C39)-1</f>
+        <v/>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Derived: the relative-purchasing-power depreciation the inflation path implies against long-run US inflation, the SAME wedge that carries the dollar debt in that year</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Egyptian pounds per US dollar — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>EGP/US$</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>57.85282682627439</v>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian pounds per US dollar — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>EGP/US$</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="n">
-        <v>59.32174625741027</v>
+      <c r="C41" s="11">
+        <f>'Assumptions'!C38*(1+'Assumptions'!C40)</f>
+        <v/>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
+          <t>Derived: the prior year's rate carried on that year's wedge</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Egyptian pounds per US dollar — FY2030/31</t>
+          <t>Currency wedge — FY2027/28</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>EGP/US$</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="n">
-        <v>60.82796247097733</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C42" s="16">
+        <f>(1+'Assumptions'!C85)/(1+'Assumptions'!C39)-1</f>
+        <v/>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Derived: the spot rate compounded at the relative-purchasing-power wedge against the model's own inflation path, year by year</t>
+          <t>Derived: the relative-purchasing-power depreciation the inflation path implies against long-run US inflation, the SAME wedge that carries the dollar debt in that year</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Export duty</t>
+          <t>Egyptian pounds per US dollar — FY2027/28</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>% of export value</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="n">
-        <v>0.1</v>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C43" s="11">
+        <f>'Assumptions'!C41*(1+'Assumptions'!C42)</f>
+        <v/>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026 replacement of the shortfall levy with an ad-valorem duty tied to the global price</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1">
+          <t>Derived: the prior year's rate carried on that year's wedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Subsidised price — FY2026/27</t>
+          <t>Currency wedge — FY2028/29</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>7526</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C44" s="16">
+        <f>(1+'Assumptions'!C86)/(1+'Assumptions'!C39)-1</f>
+        <v/>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+          <t>Derived: the relative-purchasing-power depreciation the inflation path implies against long-run US inflation, the SAME wedge that carries the dollar debt in that year</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Subsidised price — FY2027/28</t>
+          <t>Egyptian pounds per US dollar — FY2028/29</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="n">
-        <v>8429</v>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C45" s="11">
+        <f>'Assumptions'!C43*(1+'Assumptions'!C44)</f>
+        <v/>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="14" customHeight="1">
+          <t>Derived: the prior year's rate carried on that year's wedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Subsidised price — FY2028/29</t>
+          <t>Currency wedge — FY2029/30</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>EGP/tonne</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="n">
-        <v>9272</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C46" s="16">
+        <f>(1+'Assumptions'!C87)/(1+'Assumptions'!C39)-1</f>
+        <v/>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+          <t>Derived: the relative-purchasing-power depreciation the inflation path implies against long-run US inflation, the SAME wedge that carries the dollar debt in that year</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>Egyptian pounds per US dollar — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C47" s="11">
+        <f>'Assumptions'!C45*(1+'Assumptions'!C46)</f>
+        <v/>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Derived: the prior year's rate carried on that year's wedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Currency wedge — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C48" s="16">
+        <f>(1+'Assumptions'!C88)/(1+'Assumptions'!C39)-1</f>
+        <v/>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Derived: the relative-purchasing-power depreciation the inflation path implies against long-run US inflation, the SAME wedge that carries the dollar debt in that year</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Egyptian pounds per US dollar — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>EGP/US$</t>
+        </is>
+      </c>
+      <c r="C49" s="11">
+        <f>'Assumptions'!C47*(1+'Assumptions'!C48)</f>
+        <v/>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Derived: the prior year's rate carried on that year's wedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Export duty</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>% of export value</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>2026 replacement of the shortfall levy with an ad-valorem duty tied to the global price</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Subsidised price — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>EGP/tonne</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>7526</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Subsidised price — FY2027/28</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>EGP/tonne</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>8429</v>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Subsidised price — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>EGP/tonne</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>9272</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
           <t>Subsidised price — FY2029/30</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>EGP/tonne</t>
         </is>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C54" s="13" t="n">
         <v>10106</v>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Subsidised price — FY2030/31</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>EGP/tonne</t>
         </is>
       </c>
-      <c r="C48" s="13" t="n">
+      <c r="C55" s="13" t="n">
         <v>10915</v>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Constructed: administered subsidised price path from the EGP 6,000 cooperative supply price.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Local free price as % of export parity</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C49" s="15" t="n">
+      <c r="C56" s="15" t="n">
         <v>0.9</v>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Constructed: local free-market urea clears at about 90% of export parity, implied by the FY2024/25 note-20 local revenue net of the subsidised and nitrate legs</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Nitrate volume — FY2026/27</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C50" s="13" t="n">
+      <c r="C57" s="13" t="n">
         <v>26000</v>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Nitrate volume — FY2027/28</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C58" s="13" t="n">
         <v>26000</v>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Nitrate volume — FY2028/29</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C59" s="13" t="n">
         <v>26000</v>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Nitrate volume — FY2029/30</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C53" s="13" t="n">
+      <c r="C60" s="13" t="n">
         <v>26000</v>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Nitrate volume — FY2030/31</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n">
+      <c r="C61" s="13" t="n">
         <v>26000</v>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>Constructed: nitrate volume path, flat on the FY2024/25 combined granulated and low-density output.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Nitrate price, FY2024/25 basis</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>EGP/tonne</t>
         </is>
       </c>
-      <c r="C55" s="13" t="n">
+      <c r="C62" s="13" t="n">
         <v>20000</v>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>Implied by the note-20 local revenue net of the subsidised and free-market urea legs; indexed forward on the currency</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Other revenue — FY2026/27</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C56" s="20" t="n">
+      <c r="C63" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Other revenue — FY2027/28</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C57" s="20" t="n">
+      <c r="C64" s="20" t="n">
         <v>152</v>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Other revenue — FY2028/29</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="n">
-        <v>163</v>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Other revenue — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="n">
-        <v>174</v>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Other revenue — FY2030/31</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="n">
-        <v>186</v>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>COST STACK — ONE ESCALATOR PER PHYSICAL DRIVER</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Gas per tonne of ammonia</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="n">
-        <v>1292</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>Constructed and FLAGGED: the statements give a single materials line and do not split gas from the rest. Gas is set at three quarters of that line, which implies 1,292 m3 per tonne of ammonia — inside the auditor's own disclosed 1,025 to 1,771 range. This is the largest modelled allocation in the study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Realised gas price</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>US$/mmBtu</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: the company's own Q1 disclosure values 31,313,235 m3 of lost gas at EGP 251m, or EGP 8.016/m3, which converts to about US$4.68/mmBtu at the prevailing rate — below the US$5.75 contract price, which the study carries as its downside case</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
+          <t>Other revenue — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="n">
+        <v>163</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Other revenue — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="n">
+        <v>174</v>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Other revenue — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="n">
+        <v>186</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: merchant nitric acid, the ferrosilicon plant's rent and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>COST STACK — ONE ESCALATOR PER PHYSICAL DRIVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Gas per tonne of ammonia</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="n">
+        <v>1292</v>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Constructed and FLAGGED: the statements give a single materials line and do not split gas from the rest. Gas is set at three quarters of that line, which implies 1,292 m3 per tonne of ammonia — inside the auditor's own disclosed 1,025 to 1,771 range. This is the largest modelled allocation in the study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Realised gas price</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>US$/mmBtu</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: the company's own Q1 disclosure values 31,313,235 m3 of lost gas at EGP 251m, or EGP 8.016/m3, which converts to about US$4.68/mmBtu at the prevailing rate — below the US$5.75 contract price, which the study carries as its downside case</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
           <t>Energy conversion</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>mmBtu per m3</t>
         </is>
       </c>
-      <c r="C65" s="22" t="n">
+      <c r="C72" s="22" t="n">
         <v>0.03531</v>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>Constructed: standard gross calorific conversion</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Other materials per tonne of urea</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="n">
-        <v>2141.977268521675</v>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>The FY2024/25 materials line less modelled gas, over urea output: packaging, catalysts and consumable spares</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Wages in cost of sales, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C67" s="20" t="n">
-        <v>212.857</v>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Purchased services, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C68" s="20" t="n">
-        <v>62.557</v>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Inland freight per export tonne</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="n">
-        <v>1741.725316670984</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 freight and commissions over the implied export tonnage</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Other selling cost, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="n">
-        <v>176.305</v>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 selling materials, wages and other selling expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Administrative expense, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="n">
-        <v>359.624</v>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), income statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Stoppage and abnormal gas cost — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C72" s="20" t="n">
-        <v>150</v>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal gas cost — FY2027/28</t>
+          <t>Other materials per tonne of urea</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C73" s="20" t="n">
-        <v>120</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="n">
+        <v>2141.977268521675</v>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+          <t>The FY2024/25 materials line less modelled gas, over urea output: packaging, catalysts and consumable spares</t>
         </is>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal gas cost — FY2028/29</t>
+          <t>Wages in cost of sales, FY2024/25</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -5467,18 +5496,18 @@
         </is>
       </c>
       <c r="C74" s="20" t="n">
-        <v>100</v>
+        <v>212.857</v>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
         </is>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Stoppage and abnormal gas cost — FY2029/30</t>
+          <t>Purchased services, FY2024/25</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -5487,338 +5516,346 @@
         </is>
       </c>
       <c r="C75" s="20" t="n">
-        <v>90</v>
+        <v>62.557</v>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 21</t>
         </is>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
+          <t>Inland freight per export tonne</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="n">
+        <v>1741.725316670984</v>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 freight and commissions over the implied export tonnage</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Other selling cost, FY2024/25</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="n">
+        <v>176.305</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 22 selling materials, wages and other selling expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Administrative expense, FY2024/25</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="n">
+        <v>359.624</v>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), income statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2027/28</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="n">
+        <v>120</v>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Stoppage and abnormal gas cost — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
           <t>Stoppage and abnormal gas cost — FY2030/31</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C76" s="20" t="n">
+      <c r="C83" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>Constructed: stoppage and abnormal-gas cost, decaying as supply normalises from the EGP 164.5m charged in FY2024/25.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="48" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2026/27</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C77" s="15" t="n">
+      <c r="C84" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="48" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2027/28</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C78" s="15" t="n">
+      <c r="C85" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
+    <row r="86" ht="48" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2028/29</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C79" s="15" t="n">
+      <c r="C86" s="15" t="n">
         <v>0.06</v>
       </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="87" ht="48" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2029/30</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C80" s="15" t="n">
+      <c r="C87" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D87" s="9" t="inlineStr">
         <is>
           <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="48" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2030/31</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C81" s="15" t="n">
+      <c r="C88" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="D81" s="9" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>COST OF CAPITAL</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>Observed ten-year government yield</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C84" s="23" t="n">
+      <c r="C91" s="23" t="n">
         <v>0.23</v>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>Egypt ten-year government bond yield, market quote</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>Sovereign default spread, rating basis</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C85" s="23" t="n">
+      <c r="C92" s="23" t="n">
         <v>0.06372478453347744</v>
       </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="D92" s="9" t="inlineStr">
         <is>
           <t>Country risk premium workbook, original file, Egypt row, adjusted default spread</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>Normalised risk-free rate, rating basis</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C86" s="16">
-        <f>'Assumptions'!C84-'Assumptions'!C85</f>
-        <v/>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
+      <c r="C93" s="16">
+        <f>'Assumptions'!C91-'Assumptions'!C92</f>
+        <v/>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>Country risk enters ONCE, through the premium below. Using the raw local yield with a country-loaded premium would charge Egypt's sovereign risk twice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Equity risk premium, rating basis</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C87" s="23" t="n">
-        <v>0.139376943200201</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>Country risk premium workbook, original file, Egypt row, rating basis total equity risk premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Sovereign default spread, CDS basis</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C88" s="23" t="n">
-        <v>0.0341</v>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>Country risk premium workbook, original file, Egypt row, ten-year CDS spread</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Equity risk premium, CDS basis</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>Country risk premium workbook, original file, Egypt row, equity risk premium based on the sovereign credit default swap. CORRECTED 9 August 2026: the study had 9.4247%, reconstructed from a 3.55% spread the file does not carry. Damodaran's Egypt row reads 3.41% and 9.41%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C90" s="21" t="n">
-        <v>1.030210306988178</v>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>Own-stock weekly regression, 253 observations over 4.9 years against the published EGX30 index (as of 2026-07-22), R-squared 0.250, standard error 0.191, 90% interval 0.72 to 1.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Cost of equity, rating basis</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C91" s="16">
-        <f>'Assumptions'!C86+'Assumptions'!C90*'Assumptions'!C87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Cost of equity, CDS basis</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C92" s="16">
-        <f>'Assumptions'!C84-'Assumptions'!C88+'Assumptions'!C90*'Assumptions'!C89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="24" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt, local currency</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C93" s="23" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: EGP 96,896,001 of interest on the EGP 500,000,000 holding-company facility drawn in FY2024/25 — the company's own latest local borrowing</t>
         </is>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt, dollar tranche, in dollars</t>
+          <t>Equity risk premium, rating basis</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -5827,18 +5864,18 @@
         </is>
       </c>
       <c r="C94" s="23" t="n">
-        <v>0.117</v>
+        <v>0.139376943200201</v>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Constructed: EGP 1,338.0m of FY2024/25 interest on a mean dollar balance of about US$233m</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="60" customHeight="1">
+          <t>Country risk premium workbook, original file, Egypt row, rating basis total equity risk premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="14" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Expected currency depreciation</t>
+          <t>Sovereign default spread, CDS basis</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -5847,18 +5884,18 @@
         </is>
       </c>
       <c r="C95" s="23" t="n">
-        <v>0.025390625</v>
+        <v>0.0341</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Constructed: the central bank's LONG-RUN 5% target against about 2.4% in the United States, on the same relative-purchasing-power identity the study states. CORRECTED 9 August 2026: the study previously asserted 4.5% flat while stating a derivation that produces a different number in every year. The wedge is now computed from the identity rather than asserted, and the currency path is built from it year by year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
+          <t>Country risk premium workbook, original file, Egypt row, ten-year CDS spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Dollar debt at local-equivalent cost</t>
+          <t>Equity risk premium, CDS basis</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -5866,35 +5903,39 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C96" s="16">
-        <f>(1+'Assumptions'!C94)*(1+'Assumptions'!C95)-1</f>
-        <v/>
+      <c r="C96" s="23" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Country risk premium workbook, original file, Egypt row, equity risk premium based on the sovereign credit default swap. CORRECTED 9 August 2026: the study had 9.4247%, reconstructed from a 3.55% spread the file does not carry. Damodaran's Egypt row reads 3.41% and 9.41%.</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Share of debt in local currency</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="n">
-        <v>0.003135811265216677</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="n">
+        <v>1.030210306988178</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>The pound tranche of the project loan was repaid in June 2024, so the book is almost entirely dollar</t>
+          <t>Own-stock weekly regression, 253 observations over 4.9 years against the published EGX30 index (as of 2026-07-22), R-squared 0.250, standard error 0.191, 90% interval 0.72 to 1.34</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Blended pre-tax cost of debt</t>
+          <t>Cost of equity, rating basis</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -5903,14 +5944,14 @@
         </is>
       </c>
       <c r="C98" s="16">
-        <f>'Assumptions'!C97*'Assumptions'!C93+(1-'Assumptions'!C97)*'Assumptions'!C96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="24" customHeight="1">
+        <f>'Assumptions'!C93+'Assumptions'!C97*'Assumptions'!C94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Tax rate</t>
+          <t>Cost of equity, CDS basis</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -5918,19 +5959,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C99" s="15" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-16 income tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="14" customHeight="1">
+      <c r="C99" s="16">
+        <f>'Assumptions'!C91-'Assumptions'!C95+'Assumptions'!C97*'Assumptions'!C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="24" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Equity weight</t>
+          <t>Cost of debt, local currency</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -5938,19 +5975,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C100" s="15" t="n">
-        <v>0.6548338567778519</v>
+      <c r="C100" s="23" t="n">
+        <v>0.194</v>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Market-value equity over market-value equity plus debt</t>
+          <t>Constructed: EGP 96,896,001 of interest on the EGP 500,000,000 holding-company facility drawn in FY2024/25 — the company's own latest local borrowing</t>
         </is>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Debt weight</t>
+          <t>Cost of debt, dollar tranche, in dollars</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -5958,19 +5995,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C101" s="15" t="n">
-        <v>0.3451661432221481</v>
+      <c r="C101" s="23" t="n">
+        <v>0.117</v>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>One less the equity weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
+          <t>Constructed: EGP 1,338.0m of FY2024/25 interest on a mean dollar balance of about US$233m</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="60" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital, year one</t>
+          <t>Terminal currency wedge (the same identity, at the terminal inflation)</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -5978,15 +6015,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C102" s="16">
-        <f>'Assumptions'!C100*'Assumptions'!C91+'Assumptions'!C101*'Assumptions'!C98*(1-'Assumptions'!C99)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" ht="72" customHeight="1">
+      <c r="C102" s="23" t="n">
+        <v>0.025390625</v>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: the central bank's LONG-RUN 5% target against about 2.4% in the United States, on the same relative-purchasing-power identity the study states. CORRECTED 9 August 2026: the study previously asserted 4.5% flat while stating a derivation that produces a different number in every year. The wedge is now computed from the identity rather than asserted, and the currency path is built from it year by year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Terminal inflation (the same figure terminal growth is set at)</t>
+          <t>Dollar debt at local-equivalent cost, year one (FY2026/27 wedge)</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -5994,19 +6035,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C103" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>The inflation embedded in the TERMINAL discount rate: the central bank's longest-horizon published target, 5% (+/-2) for Q4 2028 — the SAME figure terminal growth is set at. CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
-        </is>
+      <c r="C103" s="16">
+        <f>(1+'Assumptions'!C101)*(1+'Assumptions'!C40)-1</f>
+        <v/>
       </c>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Long-run real rate</t>
+          <t>Share of debt in local currency</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
@@ -6015,629 +6052,761 @@
         </is>
       </c>
       <c r="C104" s="15" t="n">
-        <v>0.035</v>
+        <v>0.003139216087432172</v>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Constructed: long-run emerging-market real policy rate, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
+          <t>The pound tranche of the project loan was repaid in June 2024, so the book is almost entirely dollar</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
+          <t>Blended pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C105" s="16">
+        <f>'Assumptions'!C104*'Assumptions'!C100+(1-'Assumptions'!C104)*'Assumptions'!C103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-16 income tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Equity weight</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="n">
+        <v>0.6548330847753069</v>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Market-value equity over market-value equity plus debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Debt weight</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="n">
+        <v>0.3451669152246931</v>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>One less the equity weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Cost of capital, year one</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C109" s="16">
+        <f>'Assumptions'!C107*'Assumptions'!C98+'Assumptions'!C108*'Assumptions'!C105*(1-'Assumptions'!C106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="72" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Terminal inflation (the same figure terminal growth is set at)</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>The inflation embedded in the TERMINAL discount rate: the central bank's longest-horizon published target, 5% (+/-2) for Q4 2028 — the SAME figure terminal growth is set at. CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>Long-run real rate</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: long-run emerging-market real policy rate, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
           <t>Terminal normalised risk-free rate</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C105" s="16">
-        <f>(1+'Assumptions'!C103)*(1+'Assumptions'!C104)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="14" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+      <c r="C112" s="16">
+        <f>(1+'Assumptions'!C110)*(1+'Assumptions'!C111)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>Long-run dollar cost of debt</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C106" s="23" t="n">
+      <c r="C113" s="23" t="n">
         <v>0.09</v>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>Constructed: long-run corporate dollar cost of debt</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>Terminal cost of debt, local-equivalent</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C107" s="16">
-        <f>(1+'Assumptions'!C106)*(1+'Assumptions'!C95)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
+      <c r="C114" s="16">
+        <f>'Assumptions'!C104*'Assumptions'!C100+(1-'Assumptions'!C104)*((1+'Assumptions'!C113)*(1+'Assumptions'!C102)-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>TERMINAL COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C108" s="16">
-        <f>'Assumptions'!C100*('Assumptions'!C105+'Assumptions'!C90*'Assumptions'!C87)+'Assumptions'!C101*'Assumptions'!C107*(1-'Assumptions'!C99)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C109" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>Terminal growth set at the central bank's LONGEST-HORIZON published inflation target: 5% (+/-2) for Q4 2028. CORRECTED 9 August 2026 after external critique: the study previously used the 7% Q4-2026 target, which expires one quarter after the anchor date, as a perpetuity anchor -- and then defended it by calling 5% 'below the target', inverting the central bank's own target structure. A perpetuity takes the longest-horizon target there is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C110" s="15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: terminal return on invested capital, which sets the terminal reinvestment rate as growth divided by return on capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>CAPITAL, WORKING CAPITAL AND THE PROJECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="24" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation charge, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C113" s="20" t="n">
-        <v>771.213</v>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 6 fixed-asset register</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Amortisation, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C114" s="20" t="n">
-        <v>119.378</v>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 10 usufruct intangible</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>Project capital expenditure — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C115" s="14">
-        <f>'Cash Flow'!B30</f>
-        <v/>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
+      <c r="C115" s="16">
+        <f>'Assumptions'!C107*('Assumptions'!C112+'Assumptions'!C97*'Assumptions'!C94)+'Assumptions'!C108*'Assumptions'!C114*(1-'Assumptions'!C106)</f>
+        <v/>
       </c>
     </row>
     <row r="116" ht="60" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Project capital expenditure — FY2027/28</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C116" s="13" t="n">
-        <v>3100</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="n">
+        <v>0.05</v>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="60" customHeight="1">
+          <t>Terminal growth set at the central bank's LONGEST-HORIZON published inflation target: 5% (+/-2) for Q4 2028. CORRECTED 9 August 2026 after external critique: the study previously used the 7% Q4-2026 target, which expires one quarter after the anchor date, as a perpetuity anchor -- and then defended it by calling 5% 'below the target', inverting the central bank's own target structure. A perpetuity takes the longest-horizon target there is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Project capital expenditure — FY2028/29</t>
+          <t>Terminal return on invested capital</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C117" s="13" t="n">
-        <v>3300</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="n">
+        <v>0.18</v>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>Project capital expenditure — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C118" s="13" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Project capital expenditure — FY2030/31</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C119" s="14">
-        <f>'Cash Flow'!D34-(C115+C116+C117+C118)</f>
-        <v/>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+          <t>Constructed: terminal return on invested capital, which sets the terminal reinvestment rate as growth divided by return on capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>CAPITAL, WORKING CAPITAL AND THE PROJECT</t>
         </is>
       </c>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>Depreciation escalation on the existing base</t>
+          <t>Depreciation charge, FY2024/25</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>per year</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="n">
-        <v>0.02</v>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="n">
+        <v>771.213</v>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Constructed: escalation on the existing depreciation base, reflecting ordinary additions to the plant already in service</t>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 6 fixed-asset register</t>
         </is>
       </c>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
+          <t>Amortisation, FY2024/25</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C121" s="20" t="n">
+        <v>119.378</v>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 10 usufruct intangible</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>Project capital expenditure — FY2026/27</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C122" s="14">
+        <f>'Cash Flow'!B30</f>
+        <v/>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>Project capital expenditure — FY2027/28</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="n">
+        <v>3100</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Project capital expenditure — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Project capital expenditure — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Project capital expenditure — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C126" s="14">
+        <f>'Cash Flow'!D34-(C122+C123+C124+C125)</f>
+        <v/>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation escalation on the existing base</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: escalation on the existing depreciation base, reflecting ordinary additions to the plant already in service</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
           <t>Depreciation rate on the new complex</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>per year</t>
         </is>
       </c>
-      <c r="C121" s="23" t="n">
+      <c r="C128" s="23" t="n">
         <v>0.0395</v>
       </c>
-      <c r="D121" s="9" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-2 depreciation rates</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="48" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="129" ht="48" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>New complex nameplate</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>tonnes/day</t>
         </is>
       </c>
-      <c r="C122" s="13" t="n">
+      <c r="C129" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="D122" s="9" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
+    <row r="130" ht="24" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>Operating days a year</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C123" s="13" t="n">
+      <c r="C130" s="13" t="n">
         <v>330</v>
       </c>
-      <c r="D123" s="9" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>Constructed: operating days a year for a continuous nitrate line, net of the turnaround the company takes annually</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
+    <row r="131" ht="48" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>Steady-state depreciation wedge in the terminal year</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="C124" s="15" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: steady-state gap between the terminal inflation target and the currency wedge, held constant in the terminal year</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="C131" s="15" t="n">
+        <v>0.025390625</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED: the steady-state currency depreciation the terminal inflation (5%) implies against long-run US inflation (2.4%) on the relative purchasing-power identity — the same wedge that carries the dollar debt in the terminal year. RE-SET 1 September 2026 from a typed 2.5% so that the terminal currency, the terminal cost of debt and the last explicit year share one number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>The complex is completed and in service (1 = yes)</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
-      <c r="C125" s="13" t="n">
+      <c r="C132" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D125" s="9" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>Case switch. Zero in the capital-discipline column, where the plant is never finished and therefore never depreciated.</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="36" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>Approved cost of the new complex</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C126" s="13" t="n">
+      <c r="C133" s="13" t="n">
         <v>20341.668</v>
       </c>
-      <c r="D126" s="9" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 18-3 — bank-approved investment cost, agreement of 25 June 2025; dual-currency tranches at the approval rate</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="72" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
+    <row r="134" ht="72" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C127" s="8">
+      <c r="C134" s="8">
         <f>'Cash Flow'!D28</f>
         <v/>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D134" s="9" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure as a share of revenue, RE-ANCHORED 9 August 2026 on the company's OWN pre-project cash-flow statements: EGP 123.3m spent across FY2021/22 and FY2022/23 on EGP 11,052.9m of revenue. The first issue of this study used a 3.0% mature-plant standard instead, which is 2.7 times what this company has ever spent to keep its plant running, and which no disclosure supports. The replacement-rate framing (gross fixed assets at the disclosed 3.95% machinery rate, 6.11% of revenue) is carried as the published alternative and as the downside case.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="36" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>Wind-down cost if the programme is stopped</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C128" s="13" t="n">
+      <c r="C135" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>Constructed: capital-discipline case only: the cost of stopping the programme in the first forecast year — contract settlement and site preservation. No filing states it; it is the study's estimate and is flagged.</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="24" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>Ammonia per tonne of nitrate</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C129" s="12" t="n">
+      <c r="C136" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="D129" s="9" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
         <is>
           <t>Constructed: ammonia per tonne of ammonium nitrate through the nitric-acid route plus direct neutralisation</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Project nameplate (derived, not disclosed)</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>tonnes/year</t>
         </is>
       </c>
-      <c r="C130" s="14">
-        <f>'Assumptions'!C122*'Assumptions'!C123</f>
-        <v/>
-      </c>
-      <c r="D130" s="9" t="inlineStr">
+      <c r="C137" s="14">
+        <f>'Assumptions'!C129*'Assumptions'!C130</f>
+        <v/>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>Cross-check: nameplate derived from the ammonia surplus</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>tonnes/year</t>
         </is>
       </c>
-      <c r="C131" s="14">
-        <f>('Assumptions'!C14-'Assumptions'!C13*'Assumptions'!C15)/'Assumptions'!C129</f>
-        <v/>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
+      <c r="C138" s="14">
+        <f>('Assumptions'!C14-'Assumptions'!C13*'Assumptions'!C15)/'Assumptions'!C136</f>
+        <v/>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
         <is>
           <t>The construction the study used before the engineering award was found. Retained as a cross-check on the disclosed plate, not as the plate itself.</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="14" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>Project utilisation in the terminal year</t>
         </is>
       </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C132" s="15" t="n">
+      <c r="C139" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D139" s="9" t="inlineStr">
         <is>
           <t>Constructed: project utilisation in the terminal year, central case</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
         <is>
           <t>Nitrate price</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>US$/tonne</t>
         </is>
       </c>
-      <c r="C133" s="13" t="n">
+      <c r="C140" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="D133" s="9" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
         <is>
           <t>Mid-cycle ammonium nitrate pricing</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="14" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>Project cash margin</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C134" s="15" t="n">
+      <c r="C141" s="15" t="n">
         <v>0.32</v>
       </c>
-      <c r="D134" s="9" t="inlineStr">
+      <c r="D141" s="9" t="inlineStr">
         <is>
           <t>Constructed: conversion margin on ammonium nitrate over its own ammonia feedstock</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="14" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
         <is>
           <t>Days sales outstanding</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B142" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C135" s="20" t="n">
+      <c r="C142" s="20" t="n">
         <v>26.77469536556713</v>
       </c>
-      <c r="D135" s="9" t="inlineStr">
+      <c r="D142" s="9" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 receivables over revenue</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="14" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>Days inventory outstanding</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C136" s="20" t="n">
+      <c r="C143" s="20" t="n">
         <v>165.2475279747788</v>
       </c>
-      <c r="D136" s="9" t="inlineStr">
+      <c r="D143" s="9" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 inventory over cost of sales</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="14" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>Days payable outstanding</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C137" s="20" t="n">
+      <c r="C144" s="20" t="n">
         <v>83.17161071710899</v>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 payables over cost of sales</t>
         </is>
@@ -7077,23 +7246,23 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>'Assumptions'!C33*'Assumptions'!C38*(1-'Assumptions'!C43)</f>
+        <f>'Assumptions'!C33*'Assumptions'!C41*(1-'Assumptions'!C50)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>'Assumptions'!C34*'Assumptions'!C39*(1-'Assumptions'!C43)</f>
+        <f>'Assumptions'!C34*'Assumptions'!C43*(1-'Assumptions'!C50)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>'Assumptions'!C35*'Assumptions'!C40*(1-'Assumptions'!C43)</f>
+        <f>'Assumptions'!C35*'Assumptions'!C45*(1-'Assumptions'!C50)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>'Assumptions'!C36*'Assumptions'!C41*(1-'Assumptions'!C43)</f>
+        <f>'Assumptions'!C36*'Assumptions'!C47*(1-'Assumptions'!C50)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>'Assumptions'!C37*'Assumptions'!C42*(1-'Assumptions'!C43)</f>
+        <f>'Assumptions'!C37*'Assumptions'!C49*(1-'Assumptions'!C50)</f>
         <v/>
       </c>
     </row>
@@ -7104,23 +7273,23 @@
         </is>
       </c>
       <c r="B11" s="14">
-        <f>'Assumptions'!C33*'Assumptions'!C38*'Assumptions'!C49</f>
+        <f>'Assumptions'!C33*'Assumptions'!C41*'Assumptions'!C56</f>
         <v/>
       </c>
       <c r="C11" s="14">
-        <f>'Assumptions'!C34*'Assumptions'!C39*'Assumptions'!C49</f>
+        <f>'Assumptions'!C34*'Assumptions'!C43*'Assumptions'!C56</f>
         <v/>
       </c>
       <c r="D11" s="14">
-        <f>'Assumptions'!C35*'Assumptions'!C40*'Assumptions'!C49</f>
+        <f>'Assumptions'!C35*'Assumptions'!C45*'Assumptions'!C56</f>
         <v/>
       </c>
       <c r="E11" s="14">
-        <f>'Assumptions'!C36*'Assumptions'!C41*'Assumptions'!C49</f>
+        <f>'Assumptions'!C36*'Assumptions'!C47*'Assumptions'!C56</f>
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>'Assumptions'!C37*'Assumptions'!C42*'Assumptions'!C49</f>
+        <f>'Assumptions'!C37*'Assumptions'!C49*'Assumptions'!C56</f>
         <v/>
       </c>
     </row>
@@ -7131,23 +7300,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>'Assumptions'!C55*'Assumptions'!C38/'Assumptions'!C8</f>
+        <f>'Assumptions'!C62*'Assumptions'!C41/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>'Assumptions'!C55*'Assumptions'!C39/'Assumptions'!C8</f>
+        <f>'Assumptions'!C62*'Assumptions'!C43/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>'Assumptions'!C55*'Assumptions'!C40/'Assumptions'!C8</f>
+        <f>'Assumptions'!C62*'Assumptions'!C45/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>'Assumptions'!C55*'Assumptions'!C41/'Assumptions'!C8</f>
+        <f>'Assumptions'!C62*'Assumptions'!C47/'Assumptions'!C8</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>'Assumptions'!C55*'Assumptions'!C42/'Assumptions'!C8</f>
+        <f>'Assumptions'!C62*'Assumptions'!C49/'Assumptions'!C8</f>
         <v/>
       </c>
     </row>
@@ -7185,23 +7354,23 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>B7*'Assumptions'!C44/1000000</f>
+        <f>B7*'Assumptions'!C51/1000000</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>C7*'Assumptions'!C45/1000000</f>
+        <f>C7*'Assumptions'!C52/1000000</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>D7*'Assumptions'!C46/1000000</f>
+        <f>D7*'Assumptions'!C53/1000000</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>E7*'Assumptions'!C47/1000000</f>
+        <f>E7*'Assumptions'!C54/1000000</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>F7*'Assumptions'!C48/1000000</f>
+        <f>F7*'Assumptions'!C55/1000000</f>
         <v/>
       </c>
     </row>
@@ -7239,23 +7408,23 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>'Assumptions'!C50*B12/1000000</f>
+        <f>'Assumptions'!C57*B12/1000000</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>'Assumptions'!C51*C12/1000000</f>
+        <f>'Assumptions'!C58*C12/1000000</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>'Assumptions'!C52*D12/1000000</f>
+        <f>'Assumptions'!C59*D12/1000000</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>'Assumptions'!C53*E12/1000000</f>
+        <f>'Assumptions'!C60*E12/1000000</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>'Assumptions'!C54*F12/1000000</f>
+        <f>'Assumptions'!C61*F12/1000000</f>
         <v/>
       </c>
     </row>
@@ -7266,23 +7435,23 @@
         </is>
       </c>
       <c r="B17" s="14">
-        <f>'Assumptions'!C56</f>
+        <f>'Assumptions'!C63</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>'Assumptions'!C57</f>
+        <f>'Assumptions'!C64</f>
         <v/>
       </c>
       <c r="D17" s="14">
-        <f>'Assumptions'!C58</f>
+        <f>'Assumptions'!C65</f>
         <v/>
       </c>
       <c r="E17" s="14">
-        <f>'Assumptions'!C59</f>
+        <f>'Assumptions'!C66</f>
         <v/>
       </c>
       <c r="F17" s="14">
-        <f>'Assumptions'!C60</f>
+        <f>'Assumptions'!C67</f>
         <v/>
       </c>
     </row>
@@ -7320,23 +7489,23 @@
         </is>
       </c>
       <c r="B19" s="11">
-        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C38</f>
+        <f>'Assumptions'!C71*'Assumptions'!C72*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="C19" s="11">
-        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C39</f>
+        <f>'Assumptions'!C71*'Assumptions'!C72*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="D19" s="11">
-        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C40</f>
+        <f>'Assumptions'!C71*'Assumptions'!C72*'Assumptions'!C45</f>
         <v/>
       </c>
       <c r="E19" s="11">
-        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C41</f>
+        <f>'Assumptions'!C71*'Assumptions'!C72*'Assumptions'!C47</f>
         <v/>
       </c>
       <c r="F19" s="11">
-        <f>'Assumptions'!C64*'Assumptions'!C65*'Assumptions'!C42</f>
+        <f>'Assumptions'!C71*'Assumptions'!C72*'Assumptions'!C49</f>
         <v/>
       </c>
     </row>
@@ -7347,23 +7516,23 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>B6*'Assumptions'!C63*B19/1000000</f>
+        <f>B6*'Assumptions'!C70*B19/1000000</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>C6*'Assumptions'!C63*C19/1000000</f>
+        <f>C6*'Assumptions'!C70*C19/1000000</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>D6*'Assumptions'!C63*D19/1000000</f>
+        <f>D6*'Assumptions'!C70*D19/1000000</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>E6*'Assumptions'!C63*E19/1000000</f>
+        <f>E6*'Assumptions'!C70*E19/1000000</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>F6*'Assumptions'!C63*F19/1000000</f>
+        <f>F6*'Assumptions'!C70*F19/1000000</f>
         <v/>
       </c>
     </row>
@@ -7374,23 +7543,23 @@
         </is>
       </c>
       <c r="B21" s="19">
-        <f>(1+'Assumptions'!C77)</f>
+        <f>(1+'Assumptions'!C84)</f>
         <v/>
       </c>
       <c r="C21" s="19">
-        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)</f>
+        <f>(1+'Assumptions'!C84)*(1+'Assumptions'!C85)</f>
         <v/>
       </c>
       <c r="D21" s="19">
-        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)*(1+'Assumptions'!C79)</f>
+        <f>(1+'Assumptions'!C84)*(1+'Assumptions'!C85)*(1+'Assumptions'!C86)</f>
         <v/>
       </c>
       <c r="E21" s="19">
-        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)*(1+'Assumptions'!C79)*(1+'Assumptions'!C80)</f>
+        <f>(1+'Assumptions'!C84)*(1+'Assumptions'!C85)*(1+'Assumptions'!C86)*(1+'Assumptions'!C87)</f>
         <v/>
       </c>
       <c r="F21" s="19">
-        <f>(1+'Assumptions'!C77)*(1+'Assumptions'!C78)*(1+'Assumptions'!C79)*(1+'Assumptions'!C80)*(1+'Assumptions'!C81)</f>
+        <f>(1+'Assumptions'!C84)*(1+'Assumptions'!C85)*(1+'Assumptions'!C86)*(1+'Assumptions'!C87)*(1+'Assumptions'!C88)</f>
         <v/>
       </c>
     </row>
@@ -7401,23 +7570,23 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>B5*'Assumptions'!C66*B21/1000000</f>
+        <f>B5*'Assumptions'!C73*B21/1000000</f>
         <v/>
       </c>
       <c r="C22" s="14">
-        <f>C5*'Assumptions'!C66*C21/1000000</f>
+        <f>C5*'Assumptions'!C73*C21/1000000</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>D5*'Assumptions'!C66*D21/1000000</f>
+        <f>D5*'Assumptions'!C73*D21/1000000</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>E5*'Assumptions'!C66*E21/1000000</f>
+        <f>E5*'Assumptions'!C73*E21/1000000</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>F5*'Assumptions'!C66*F21/1000000</f>
+        <f>F5*'Assumptions'!C73*F21/1000000</f>
         <v/>
       </c>
     </row>
@@ -7428,23 +7597,23 @@
         </is>
       </c>
       <c r="B23" s="14">
-        <f>'Assumptions'!C67*B21</f>
+        <f>'Assumptions'!C74*B21</f>
         <v/>
       </c>
       <c r="C23" s="14">
-        <f>'Assumptions'!C67*C21</f>
+        <f>'Assumptions'!C74*C21</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>'Assumptions'!C67*D21</f>
+        <f>'Assumptions'!C74*D21</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>'Assumptions'!C67*E21</f>
+        <f>'Assumptions'!C74*E21</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>'Assumptions'!C67*F21</f>
+        <f>'Assumptions'!C74*F21</f>
         <v/>
       </c>
     </row>
@@ -7455,23 +7624,23 @@
         </is>
       </c>
       <c r="B24" s="14">
-        <f>'Assumptions'!C68*B21</f>
+        <f>'Assumptions'!C75*B21</f>
         <v/>
       </c>
       <c r="C24" s="14">
-        <f>'Assumptions'!C68*C21</f>
+        <f>'Assumptions'!C75*C21</f>
         <v/>
       </c>
       <c r="D24" s="14">
-        <f>'Assumptions'!C68*D21</f>
+        <f>'Assumptions'!C75*D21</f>
         <v/>
       </c>
       <c r="E24" s="14">
-        <f>'Assumptions'!C68*E21</f>
+        <f>'Assumptions'!C75*E21</f>
         <v/>
       </c>
       <c r="F24" s="14">
-        <f>'Assumptions'!C68*F21</f>
+        <f>'Assumptions'!C75*F21</f>
         <v/>
       </c>
     </row>
@@ -7482,23 +7651,23 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>'Assumptions'!C113*(1+'Assumptions'!C120*0)+'Assumptions'!C114</f>
+        <f>'Assumptions'!C120*(1+'Assumptions'!C127*0)+'Assumptions'!C121</f>
         <v/>
       </c>
       <c r="C25" s="14">
-        <f>'Assumptions'!C113*(1+'Assumptions'!C120*1)+'Assumptions'!C114+SUM('Assumptions'!C115:C115)*'Assumptions'!C121</f>
+        <f>'Assumptions'!C120*(1+'Assumptions'!C127*1)+'Assumptions'!C121+SUM('Assumptions'!C122:C122)*'Assumptions'!C128</f>
         <v/>
       </c>
       <c r="D25" s="14">
-        <f>'Assumptions'!C113*(1+'Assumptions'!C120*2)+'Assumptions'!C114+SUM('Assumptions'!C115:C116)*'Assumptions'!C121</f>
+        <f>'Assumptions'!C120*(1+'Assumptions'!C127*2)+'Assumptions'!C121+SUM('Assumptions'!C122:C123)*'Assumptions'!C128</f>
         <v/>
       </c>
       <c r="E25" s="14">
-        <f>'Assumptions'!C113*(1+'Assumptions'!C120*3)+'Assumptions'!C114+SUM('Assumptions'!C115:C117)*'Assumptions'!C121</f>
+        <f>'Assumptions'!C120*(1+'Assumptions'!C127*3)+'Assumptions'!C121+SUM('Assumptions'!C122:C124)*'Assumptions'!C128</f>
         <v/>
       </c>
       <c r="F25" s="14">
-        <f>'Assumptions'!C113*(1+'Assumptions'!C120*4)+'Assumptions'!C114+SUM('Assumptions'!C115:C118)*'Assumptions'!C121</f>
+        <f>'Assumptions'!C120*(1+'Assumptions'!C127*4)+'Assumptions'!C121+SUM('Assumptions'!C122:C125)*'Assumptions'!C128</f>
         <v/>
       </c>
     </row>
@@ -7590,23 +7759,23 @@
         </is>
       </c>
       <c r="B29" s="14">
-        <f>B9*'Assumptions'!C69*B21/1000000</f>
+        <f>B9*'Assumptions'!C76*B21/1000000</f>
         <v/>
       </c>
       <c r="C29" s="14">
-        <f>C9*'Assumptions'!C69*C21/1000000</f>
+        <f>C9*'Assumptions'!C76*C21/1000000</f>
         <v/>
       </c>
       <c r="D29" s="14">
-        <f>D9*'Assumptions'!C69*D21/1000000</f>
+        <f>D9*'Assumptions'!C76*D21/1000000</f>
         <v/>
       </c>
       <c r="E29" s="14">
-        <f>E9*'Assumptions'!C69*E21/1000000</f>
+        <f>E9*'Assumptions'!C76*E21/1000000</f>
         <v/>
       </c>
       <c r="F29" s="14">
-        <f>F9*'Assumptions'!C69*F21/1000000</f>
+        <f>F9*'Assumptions'!C76*F21/1000000</f>
         <v/>
       </c>
     </row>
@@ -7617,23 +7786,23 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>'Assumptions'!C70*B21</f>
+        <f>'Assumptions'!C77*B21</f>
         <v/>
       </c>
       <c r="C30" s="14">
-        <f>'Assumptions'!C70*C21</f>
+        <f>'Assumptions'!C77*C21</f>
         <v/>
       </c>
       <c r="D30" s="14">
-        <f>'Assumptions'!C70*D21</f>
+        <f>'Assumptions'!C77*D21</f>
         <v/>
       </c>
       <c r="E30" s="14">
-        <f>'Assumptions'!C70*E21</f>
+        <f>'Assumptions'!C77*E21</f>
         <v/>
       </c>
       <c r="F30" s="14">
-        <f>'Assumptions'!C70*F21</f>
+        <f>'Assumptions'!C77*F21</f>
         <v/>
       </c>
     </row>
@@ -7644,23 +7813,23 @@
         </is>
       </c>
       <c r="B31" s="14">
-        <f>'Assumptions'!C71*B21</f>
+        <f>'Assumptions'!C78*B21</f>
         <v/>
       </c>
       <c r="C31" s="14">
-        <f>'Assumptions'!C71*C21</f>
+        <f>'Assumptions'!C78*C21</f>
         <v/>
       </c>
       <c r="D31" s="14">
-        <f>'Assumptions'!C71*D21</f>
+        <f>'Assumptions'!C78*D21</f>
         <v/>
       </c>
       <c r="E31" s="14">
-        <f>'Assumptions'!C71*E21</f>
+        <f>'Assumptions'!C78*E21</f>
         <v/>
       </c>
       <c r="F31" s="14">
-        <f>'Assumptions'!C71*F21</f>
+        <f>'Assumptions'!C78*F21</f>
         <v/>
       </c>
     </row>
@@ -7671,23 +7840,23 @@
         </is>
       </c>
       <c r="B32" s="14">
-        <f>'Assumptions'!C72</f>
+        <f>'Assumptions'!C79</f>
         <v/>
       </c>
       <c r="C32" s="14">
-        <f>'Assumptions'!C73</f>
+        <f>'Assumptions'!C80</f>
         <v/>
       </c>
       <c r="D32" s="14">
-        <f>'Assumptions'!C74</f>
+        <f>'Assumptions'!C81</f>
         <v/>
       </c>
       <c r="E32" s="14">
-        <f>'Assumptions'!C75</f>
+        <f>'Assumptions'!C82</f>
         <v/>
       </c>
       <c r="F32" s="14">
-        <f>'Assumptions'!C76</f>
+        <f>'Assumptions'!C83</f>
         <v/>
       </c>
     </row>
@@ -8087,7 +8256,7 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>B22*B23*B24*(1-'Assumptions'!C43)/1000000</f>
+        <f>B22*B23*B24*(1-'Assumptions'!C50)/1000000</f>
         <v/>
       </c>
       <c r="C25" s="9" t="inlineStr"/>
@@ -8153,7 +8322,7 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>(B29-'Assumptions'!C113-'Assumptions'!C114)*(1-'Assumptions'!C99)</f>
+        <f>(B29-'Assumptions'!C120-'Assumptions'!C121)*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -8435,23 +8604,23 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>B9*(1-'Assumptions'!C99)</f>
+        <f>B9*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>C9*(1-'Assumptions'!C99)</f>
+        <f>C9*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>D9*(1-'Assumptions'!C99)</f>
+        <f>D9*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>E9*(1-'Assumptions'!C99)</f>
+        <f>E9*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>F9*(1-'Assumptions'!C99)</f>
+        <f>F9*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
     </row>
@@ -8489,23 +8658,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>-($I$5*'Assumptions'!C115+$I$6*(1-$I$5)+B5*'Assumptions'!C127)</f>
+        <f>-($I$5*'Assumptions'!C122+$I$6*(1-$I$5)+B5*'Assumptions'!C134)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>-($I$5*'Assumptions'!C116+C5*'Assumptions'!C127)</f>
+        <f>-($I$5*'Assumptions'!C123+C5*'Assumptions'!C134)</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>-($I$5*'Assumptions'!C117+D5*'Assumptions'!C127)</f>
+        <f>-($I$5*'Assumptions'!C124+D5*'Assumptions'!C134)</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>-($I$5*'Assumptions'!C118+E5*'Assumptions'!C127)</f>
+        <f>-($I$5*'Assumptions'!C125+E5*'Assumptions'!C134)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>-($I$5*'Assumptions'!C119+F5*'Assumptions'!C127)</f>
+        <f>-($I$5*'Assumptions'!C126+F5*'Assumptions'!C134)</f>
         <v/>
       </c>
     </row>
@@ -8570,23 +8739,23 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*0/5</f>
+        <f>'Assumptions'!C109</f>
         <v/>
       </c>
       <c r="C15" s="27">
-        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*1/5</f>
+        <f>'Assumptions'!C107*(('Assumptions'!C93+('Assumptions'!C112-'Assumptions'!C93)*1/5)+'Assumptions'!C97*'Assumptions'!C94)+'Assumptions'!C108*('Assumptions'!C104*'Assumptions'!C100+(1-'Assumptions'!C104)*((1+'Assumptions'!C101)*(1+'Assumptions'!C42)-1))*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="D15" s="27">
-        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*2/5</f>
+        <f>'Assumptions'!C107*(('Assumptions'!C93+('Assumptions'!C112-'Assumptions'!C93)*2/5)+'Assumptions'!C97*'Assumptions'!C94)+'Assumptions'!C108*('Assumptions'!C104*'Assumptions'!C100+(1-'Assumptions'!C104)*((1+'Assumptions'!C101)*(1+'Assumptions'!C44)-1))*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*3/5</f>
+        <f>'Assumptions'!C107*(('Assumptions'!C93+('Assumptions'!C112-'Assumptions'!C93)*3/5)+'Assumptions'!C97*'Assumptions'!C94)+'Assumptions'!C108*('Assumptions'!C104*'Assumptions'!C100+(1-'Assumptions'!C104)*((1+'Assumptions'!C101)*(1+'Assumptions'!C46)-1))*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>'Assumptions'!C102+('Assumptions'!C108-'Assumptions'!C102)*4/5</f>
+        <f>'Assumptions'!C107*(('Assumptions'!C93+('Assumptions'!C112-'Assumptions'!C93)*4/5)+'Assumptions'!C97*'Assumptions'!C94)+'Assumptions'!C108*('Assumptions'!C104*'Assumptions'!C100+(1-'Assumptions'!C104)*((1+'Assumptions'!C101)*(1+'Assumptions'!C48)-1))*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
     </row>
@@ -8672,11 +8841,11 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>F9*(1+'Assumptions'!C109)</f>
+        <f>F9*(1+'Assumptions'!C116)</f>
         <v/>
       </c>
       <c r="D21" s="14">
-        <f>(F9+SUM('Assumptions'!C115:C118)*'Assumptions'!C121)*(1+'Assumptions'!C109)</f>
+        <f>(F9+SUM('Assumptions'!C122:C125)*'Assumptions'!C128)*(1+'Assumptions'!C116)</f>
         <v/>
       </c>
     </row>
@@ -8687,11 +8856,11 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>'Assumptions'!C130*'Assumptions'!C132*'Assumptions'!C133*('Assumptions'!C42*(1+'Assumptions'!C109-'Assumptions'!C124))/1000000</f>
+        <f>'Assumptions'!C137*'Assumptions'!C139*'Assumptions'!C140*('Assumptions'!C49*(1+'Assumptions'!C116-'Assumptions'!C131))/1000000</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>'Assumptions'!C130*0*'Assumptions'!C133*('Assumptions'!C42*(1+'Assumptions'!C109-'Assumptions'!C124))/1000000</f>
+        <f>'Assumptions'!C137*0*'Assumptions'!C140*('Assumptions'!C49*(1+'Assumptions'!C116-'Assumptions'!C131))/1000000</f>
         <v/>
       </c>
     </row>
@@ -8702,11 +8871,11 @@
         </is>
       </c>
       <c r="B23" s="14">
-        <f>B22*'Assumptions'!C134-'Assumptions'!C125*'Assumptions'!C126*'Assumptions'!C121</f>
+        <f>B22*'Assumptions'!C141-'Assumptions'!C132*'Assumptions'!C133*'Assumptions'!C128</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>D22*'Assumptions'!C134-0*'Assumptions'!C126*'Assumptions'!C121</f>
+        <f>D22*'Assumptions'!C141-0*'Assumptions'!C133*'Assumptions'!C128</f>
         <v/>
       </c>
     </row>
@@ -8732,11 +8901,11 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>B24*(1-'Assumptions'!C99)</f>
+        <f>B24*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
       <c r="D25" s="14">
-        <f>D24*(1-'Assumptions'!C99)</f>
+        <f>D24*(1-'Assumptions'!C106)</f>
         <v/>
       </c>
     </row>
@@ -8747,11 +8916,11 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>'Assumptions'!C109/'Assumptions'!C110</f>
+        <f>'Assumptions'!C116/'Assumptions'!C117</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>'Assumptions'!C109/'Assumptions'!C110</f>
+        <f>'Assumptions'!C116/'Assumptions'!C117</f>
         <v/>
       </c>
     </row>
@@ -8777,11 +8946,11 @@
         </is>
       </c>
       <c r="B28" s="14">
-        <f>B27/('Assumptions'!C108-'Assumptions'!C109)</f>
+        <f>B27/('Assumptions'!C115-'Assumptions'!C116)</f>
         <v/>
       </c>
       <c r="D28" s="14">
-        <f>D27/('Assumptions'!C108-'Assumptions'!C109)</f>
+        <f>D27/('Assumptions'!C115-'Assumptions'!C116)</f>
         <v/>
       </c>
     </row>
@@ -9011,23 +9180,23 @@
         </is>
       </c>
       <c r="B50" s="14">
-        <f>+'Assumptions'!C115</f>
+        <f>+'Assumptions'!C122</f>
         <v/>
       </c>
       <c r="C50" s="14">
-        <f>+'Assumptions'!C116</f>
+        <f>+'Assumptions'!C123</f>
         <v/>
       </c>
       <c r="D50" s="14">
-        <f>+'Assumptions'!C117</f>
+        <f>+'Assumptions'!C124</f>
         <v/>
       </c>
       <c r="E50" s="14">
-        <f>+'Assumptions'!C118</f>
+        <f>+'Assumptions'!C125</f>
         <v/>
       </c>
       <c r="F50" s="14">
-        <f>+'Assumptions'!C119</f>
+        <f>+'Assumptions'!C126</f>
         <v/>
       </c>
     </row>
@@ -9038,7 +9207,7 @@
         </is>
       </c>
       <c r="B51" s="14">
-        <f>-'Assumptions'!C128</f>
+        <f>-'Assumptions'!C135</f>
         <v/>
       </c>
       <c r="C51" s="14">
@@ -9069,19 +9238,19 @@
         <v/>
       </c>
       <c r="C52" s="14">
-        <f>-SUM('Assumptions'!C115:C115)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <f>-SUM('Assumptions'!C122:C122)*'Assumptions'!C128*'Assumptions'!C106</f>
         <v/>
       </c>
       <c r="D52" s="14">
-        <f>-SUM('Assumptions'!C115:C116)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <f>-SUM('Assumptions'!C122:C123)*'Assumptions'!C128*'Assumptions'!C106</f>
         <v/>
       </c>
       <c r="E52" s="14">
-        <f>-SUM('Assumptions'!C115:C117)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <f>-SUM('Assumptions'!C122:C124)*'Assumptions'!C128*'Assumptions'!C106</f>
         <v/>
       </c>
       <c r="F52" s="14">
-        <f>-SUM('Assumptions'!C115:C118)*'Assumptions'!C121*'Assumptions'!C99</f>
+        <f>-SUM('Assumptions'!C122:C125)*'Assumptions'!C128*'Assumptions'!C106</f>
         <v/>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_01092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_01092026.xlsx
@@ -3437,7 +3437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3766,6 +3766,82 @@
       <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Terminal value as a share of enterprise value is reported beside the cash-flow lens on the DCF sheet, in both columns, because on this company it is the number that decides the answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>THE WEIGHTED CENTRAL INSIDE THE FIELD — stated weights, reading the lens cells above</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Weight: cash flow, programme carried through</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Weight: relative multiples</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Weight: normalised earnings power</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Weight: book value and sustainable return</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Weighted central (EGP/share)</t>
+        </is>
+      </c>
+      <c r="B38" s="11">
+        <f>B34*B5+B35*B7+B36*B8+B37*B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Against spot</t>
+        </is>
+      </c>
+      <c r="B39" s="8">
+        <f>B38/$B$14-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Only the carried-through side of the cash-flow lens enters the weighting (the company's stated plan); the stopped reading is the contested judgement above, published beside it and never averaged in. Bear and full are the field's floor and ceiling, never the weighted extremes.</t>
         </is>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_01092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_01092026.xlsx
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>13.98</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="13">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.7</v>
+        <v>-2.64</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-2.79</v>
+        <v>-2.76</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-2.89</v>
+        <v>-2.88</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>-2.95</v>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-1.19</v>
+        <v>-1.08</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-1.54</v>
+        <v>-1.51</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1.66</v>
+        <v>-1.65</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>-1.78</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.31</v>
+        <v>0.49</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="9">
@@ -2741,19 +2741,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="10">
@@ -2763,19 +2763,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3.31</v>
+        <v>3.61</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.1030999883383652</v>
+        <v>1.785377453868092</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>-1.397694934111888</v>
+        <v>0.3670158141445878</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>-0.6670180351027122</v>
+        <v>1.681839374144488</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2883,7 +2883,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>The cost of debt at the company's own disclosed rates — 19.4% on the local facility, 11.7% in dollars on the project loan carried at local-equivalent cost on the derived currency path, 20.0% in year one gliding to 11.8% at the terminal</t>
+          <t>The cost of debt at the company's own disclosed rates — 19.4% on the local facility, 11.7% in dollars on the project loan carried at local-equivalent cost on the derived currency path, 20.0% in year one gliding to 13.9% at the terminal</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>-1.062000234885711</v>
+        <v>0.9828446765320163</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.1709154866519979</v>
+        <v>2.859085724910241</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>-2.50809878104179</v>
+        <v>-0.1265904861401076</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>-0.3983876059568149</v>
+        <v>2.015514431643158</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>-1.415814469979403</v>
+        <v>0.9216105075155367</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -2978,16 +2978,16 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Terminal reinvestment of 27.8% of operating profit after tax, from growth over an 18% return on capital</t>
+          <t>Terminal reinvestment of 38.9% of operating profit after tax, from growth over an 18% return on capital</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>16.7%, from a 30% return on capital — the rate a newly completed plant earns on incremental capital while it is still filling</t>
+          <t>23.3%, from a 30% return on capital — the rate a newly completed plant earns on incremental capital while it is still filling</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>-0.3534762974524243</v>
+        <v>2.624416745702623</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>-0.8572462475446263</v>
+        <v>1.552597382184459</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>13.98</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="15">
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.07750436005742409</v>
+        <v>0.1096361607961464</v>
       </c>
     </row>
     <row r="26">
@@ -3772,76 +3772,79 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>THE WEIGHTED CENTRAL INSIDE THE FIELD — stated weights, reading the lens cells above</t>
+          <t>THE ANSWER — TWO BRANCHES, PUBLISHED SIDE BY SIDE AND NEVER AVERAGED</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Weight: cash flow, programme carried through</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n">
-        <v>0.45</v>
+          <t>Cash-flow lens — ANNA programme CARRIED THROUGH (EGP/share)</t>
+        </is>
+      </c>
+      <c r="B34" s="11">
+        <f>B5</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Weight: relative multiples</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n">
-        <v>0.2</v>
+          <t>Against spot</t>
+        </is>
+      </c>
+      <c r="B35" s="8">
+        <f>B34/$B$14-1</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Weight: normalised earnings power</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n">
-        <v>0.2</v>
+          <t>Cash-flow lens — ANNA programme STOPPED (EGP/share)</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>5.900148689005042</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Weight: book value and sustainable return</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>0.15</v>
+          <t>Against spot</t>
+        </is>
+      </c>
+      <c r="B37" s="8">
+        <f>B36/$B$14-1</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Weighted central (EGP/share)</t>
-        </is>
-      </c>
-      <c r="B38" s="11">
-        <f>B34*B5+B35*B7+B36*B8+B37*B6</f>
-        <v/>
+          <t>RETIRED — the 45/20/20/15 weighted blend, published unused</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>4.756234842977872</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Against spot</t>
-        </is>
-      </c>
-      <c r="B39" s="8">
-        <f>B38/$B$14-1</f>
-        <v/>
+          <t>Why it is retired</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>the weights were typed and had never cleared an out-of-sample test</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>Only the carried-through side of the cash-flow lens enters the weighting (the company's stated plan); the stopped reading is the contested judgement above, published beside it and never averaged in. Bear and full are the field's floor and ceiling, never the weighted extremes.</t>
+          <t>The judgement is BINARY and its two answers straddle the interesting range, so an average would describe a half-built plant — a world nobody is proposing and the company is not in. Both branches are published; neither is weighted into the other. Bear and full are the field's floor and ceiling.</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4144,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>-0.6254255245924404</v>
+        <v>1.785377453868092</v>
       </c>
     </row>
     <row r="24">
@@ -4151,17 +4154,17 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>3.427492145329595</v>
+        <v>5.900148689005042</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Book value and sustainable return</t>
+          <t>Book value, disclosed (a floor, never weighted)</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>0.5841958982966984</v>
+        <v>8.15778582586335</v>
       </c>
     </row>
     <row r="26">
@@ -4289,7 +4292,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="14" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Anchor price</t>
@@ -4301,11 +4304,11 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>13.98</v>
+        <v>14.41</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Exchange close, from the study's own price library</t>
+          <t>EGCH closing price on the Egyptian Exchange, 3 September 2026, from the prices supplied by the principal and committed at engine/prices/SUPPLIED_03-09-2026.json. [R-GAP-01 AMENDED]: no study is delivered against a stale price, and the previous 13.98 was struck on 6 August</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4766,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Export urea price — FY2026/27</t>
@@ -4779,11 +4782,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
+          <t>Held FLAT in nominal dollars at the opening level. No forecast of a traded commodity price is defensible, which is the convention this house applies to the same class of input elsewhere; the previous path fell 17% over five years on a construction nothing sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Export urea price — FY2027/28</t>
@@ -4795,15 +4798,15 @@
         </is>
       </c>
       <c r="C34" s="20" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
+          <t>Held FLAT in nominal dollars at the opening level. No forecast of a traded commodity price is defensible, which is the convention this house applies to the same class of input elsewhere; the previous path fell 17% over five years on a construction nothing sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Export urea price — FY2028/29</t>
@@ -4815,15 +4818,15 @@
         </is>
       </c>
       <c r="C35" s="20" t="n">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
+          <t>Held FLAT in nominal dollars at the opening level. No forecast of a traded commodity price is defensible, which is the convention this house applies to the same class of input elsewhere; the previous path fell 17% over five years on a construction nothing sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Export urea price — FY2029/30</t>
@@ -4835,15 +4838,15 @@
         </is>
       </c>
       <c r="C36" s="20" t="n">
-        <v>450</v>
+        <v>530</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
+          <t>Held FLAT in nominal dollars at the opening level. No forecast of a traded commodity price is defensible, which is the convention this house applies to the same class of input elsewhere; the previous path fell 17% over five years on a construction nothing sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Export urea price — FY2030/31</t>
@@ -4855,11 +4858,11 @@
         </is>
       </c>
       <c r="C37" s="20" t="n">
-        <v>440</v>
+        <v>530</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Constructed: export price path, mean-reverting from the August 2026 quote toward the cash cost of the marginal gas-based producer.</t>
+          <t>Held FLAT in nominal dollars at the opening level. No forecast of a traded commodity price is defensible, which is the convention this house applies to the same class of input elsewhere; the previous path fell 17% over five years on a construction nothing sourced.</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6095,7 @@
         </is>
       </c>
       <c r="C102" s="23" t="n">
-        <v>0.025390625</v>
+        <v>0.044921875</v>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
@@ -6184,7 +6187,7 @@
         </is>
       </c>
       <c r="C107" s="15" t="n">
-        <v>0.6548330847753069</v>
+        <v>0.6616480028913871</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
@@ -6204,7 +6207,7 @@
         </is>
       </c>
       <c r="C108" s="15" t="n">
-        <v>0.3451669152246931</v>
+        <v>0.3383519971086129</v>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
@@ -6240,7 +6243,7 @@
         </is>
       </c>
       <c r="C110" s="15" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
@@ -6260,11 +6263,11 @@
         </is>
       </c>
       <c r="C111" s="15" t="n">
-        <v>0.035</v>
+        <v>0.055</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Constructed: long-run emerging-market real policy rate, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
+          <t>The house real-rate convention, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6339,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
+    <row r="116" ht="72" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
           <t>Terminal growth</t>
@@ -6348,11 +6351,11 @@
         </is>
       </c>
       <c r="C116" s="15" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Terminal growth set at the central bank's LONGEST-HORIZON published inflation target: 5% (+/-2) for Q4 2028. CORRECTED 9 August 2026 after external critique: the study previously used the 7% Q4-2026 target, which expires one quarter after the anchor date, as a perpetuity anchor -- and then defended it by calling 5% 'below the target', inverting the central bank's own target structure. A perpetuity takes the longest-horizon target there is.</t>
+          <t>Terminal growth from the house macro path: terminal inflation plus a STATED real growth of zero, so the real assumption is written down rather than inferred from the gap to the discount rate. It was 5% (+/-2) for Q4 2028. CORRECTED 9 August 2026 after external critique: the study previously used the 7% Q4-2026 target, which expires one quarter after the anchor date, as a perpetuity anchor -- and then defended it by calling 5% 'below the target', inverting the central bank's own target structure. A perpetuity takes the longest-horizon target there is.</t>
         </is>
       </c>
     </row>
